--- a/datasets/MpesaStatement_Katra.xlsx
+++ b/datasets/MpesaStatement_Katra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/briankimanzi/Documents/programming Languages/PythonProgramming/JupyterNoteBook/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F904A26-FE06-5E44-8E0D-E63BF25190D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBE0ACB-0829-F243-9097-D05B8B443CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{5FAECA30-C9D0-45DB-B3FF-81CAF5B5014D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="169">
   <si>
     <t>Receipt No.</t>
   </si>
@@ -69,9 +69,6 @@
     <t>TD48BNDSIK</t>
   </si>
   <si>
-    <t>Pay Bill Online to 522006 SAFARICOM  HOME Acc.</t>
-  </si>
-  <si>
     <t>TCU0NDJPKK</t>
   </si>
   <si>
@@ -96,15 +93,6 @@
     <t>TCK0EATVUQ</t>
   </si>
   <si>
-    <t>Customer Transfer to -</t>
-  </si>
-  <si>
-    <t>2547******581 ABDULLAHI</t>
-  </si>
-  <si>
-    <t>SOYAN</t>
-  </si>
-  <si>
     <t>TCJ1BIKHZZ</t>
   </si>
   <si>
@@ -117,18 +105,9 @@
     <t>TCJ2BG3YTE</t>
   </si>
   <si>
-    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is</t>
-  </si>
-  <si>
     <t>TCI88RDZ2I</t>
   </si>
   <si>
-    <t>Funds received from -</t>
-  </si>
-  <si>
-    <t>2547******829 SAFIA SOYAN</t>
-  </si>
-  <si>
     <t>TCI66UNCKK</t>
   </si>
   <si>
@@ -144,18 +123,12 @@
     <t>TCE5N5UXIB</t>
   </si>
   <si>
-    <t>2547******673 NOOR DUKOW</t>
-  </si>
-  <si>
     <t>TC71RB2E57</t>
   </si>
   <si>
     <t>TC52G2OB1S</t>
   </si>
   <si>
-    <t>2547******284 EBYAN SOYAN</t>
-  </si>
-  <si>
     <t>TC44BGUFI4</t>
   </si>
   <si>
@@ -285,9 +258,6 @@
     <t>TA99KF6WRT</t>
   </si>
   <si>
-    <t>07******524 QAMAR SOYAN</t>
-  </si>
-  <si>
     <t>TA75AQPPRR</t>
   </si>
   <si>
@@ -330,18 +300,6 @@
     <t>SLH7TE5ZIB</t>
   </si>
   <si>
-    <t>Customer Withdrawal At Agent</t>
-  </si>
-  <si>
-    <t>Till 2083144 - Conran</t>
-  </si>
-  <si>
-    <t>International Precious Agencies</t>
-  </si>
-  <si>
-    <t>JUJA TOWN</t>
-  </si>
-  <si>
     <t>SLH6S8697I</t>
   </si>
   <si>
@@ -360,9 +318,6 @@
     <t>SKU6N7BYAQ</t>
   </si>
   <si>
-    <t>OMNIRIB_AB655FE80924.</t>
-  </si>
-  <si>
     <t>SKU9N6XQ4H</t>
   </si>
   <si>
@@ -384,15 +339,6 @@
     <t>SKP13NJHU9</t>
   </si>
   <si>
-    <t>Deposit of Funds at Agent Till</t>
-  </si>
-  <si>
-    <t>621103 -  LIONEX LtdJuja-Near</t>
-  </si>
-  <si>
-    <t>JKUAT</t>
-  </si>
-  <si>
     <t>SKM3OIYAG1</t>
   </si>
   <si>
@@ -423,9 +369,6 @@
     <t>SKF5WJH3NL</t>
   </si>
   <si>
-    <t>OMNIRIB_AB62BC534B24.</t>
-  </si>
-  <si>
     <t>SKC0LCF4BW</t>
   </si>
   <si>
@@ -444,30 +387,18 @@
     <t>SK105BBOHW</t>
   </si>
   <si>
-    <t>OMNIRIB_AB5FEF052824.</t>
-  </si>
-  <si>
     <t>SJU6VJB4QA</t>
   </si>
   <si>
     <t>SJU9VJ6Y8V</t>
   </si>
   <si>
-    <t>OMNIRIB_AB5F609CA824.</t>
-  </si>
-  <si>
     <t>SJP6DU6IHC</t>
   </si>
   <si>
     <t>SJO47UFH1O</t>
   </si>
   <si>
-    <t>Till 536001 - CINCINNATI</t>
-  </si>
-  <si>
-    <t>INVESTMENTS LIMITED Utawala</t>
-  </si>
-  <si>
     <t>SJO97LUI3Z</t>
   </si>
   <si>
@@ -480,30 +411,12 @@
     <t>SJN65WBA5I</t>
   </si>
   <si>
-    <t>Promotion Payment from</t>
-  </si>
-  <si>
-    <t>4090193 - M-PESA OFFERS. via</t>
-  </si>
-  <si>
-    <t>API. Orginal conversation ID is DELIGHT24_b9919a57-c399479e-af5c-5f0e63c101aa.</t>
-  </si>
-  <si>
     <t>SJN45G2KWO</t>
   </si>
   <si>
     <t>SJM1YCLW6L</t>
   </si>
   <si>
-    <t>Till 2321980 - VIEW POWER</t>
-  </si>
-  <si>
-    <t>COMMS Equity electronics Hilal</t>
-  </si>
-  <si>
-    <t>Garden Hotel</t>
-  </si>
-  <si>
     <t>SJM8Y5AW5C</t>
   </si>
   <si>
@@ -528,9 +441,6 @@
     <t>SJB2QIB142</t>
   </si>
   <si>
-    <t>OMNIRIB_AB5BBC296B24.</t>
-  </si>
-  <si>
     <t>SJB3NQVCV5</t>
   </si>
   <si>
@@ -595,6 +505,42 @@
   </si>
   <si>
     <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB6CEA166725.</t>
+  </si>
+  <si>
+    <t>Customer Withdrawal At Agent Till 2083144 - Conran International Precious Agencies JUJA TOWN</t>
+  </si>
+  <si>
+    <t>Funds received from - 07******524 QAMAR SOYAN</t>
+  </si>
+  <si>
+    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB655FE80924.</t>
+  </si>
+  <si>
+    <t>Deposit of Funds at Agent Till 621103 -  LIONEX LtdJuja-Near JKUAT</t>
+  </si>
+  <si>
+    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB62BC534B24.</t>
+  </si>
+  <si>
+    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB5FEF052824.</t>
+  </si>
+  <si>
+    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB5F609CA824.</t>
+  </si>
+  <si>
+    <t>Customer Withdrawal At Agent Till 536001 - CINCINNATI INVESTMENTS LIMITED Utawala</t>
+  </si>
+  <si>
+    <t>Promotion Payment from 4090193 - M-PESA OFFERS. Via API. Orginal conversation ID is DELIGHT24_b9919a57-c399479e-af5c-5f0e63c101aa.</t>
+  </si>
+  <si>
+    <t>Customer Transfer to - 2547******581 ABDULLAHI SOYAN</t>
+  </si>
+  <si>
+    <t>Customer Withdrawal At Agent Till 2321980 - VIEW POWER COMMS Equity electronics Hilal Garden Hotel</t>
+  </si>
+  <si>
+    <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB5BBC296B24.</t>
   </si>
 </sst>
 </file>
@@ -638,7 +584,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -723,17 +669,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF43B02A"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF43B02A"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF43B02A"/>
@@ -746,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -805,49 +740,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1167,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9DA849-ED55-4B77-82CF-6A62B5BF6ECA}">
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -1231,7 +1130,7 @@
         <v>45751.215613425928</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>9</v>
@@ -1246,13 +1145,13 @@
     </row>
     <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="16">
         <v>45746.30096064815</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>9</v>
@@ -1267,13 +1166,13 @@
     </row>
     <row r="5" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="16">
         <v>45746.30096064815</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>9</v>
@@ -1288,9 +1187,9 @@
     </row>
     <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="35">
+        <v>14</v>
+      </c>
+      <c r="B6" s="23">
         <v>45744.839895833335</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1309,7 +1208,7 @@
     </row>
     <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="20">
         <v>45744.839178240742</v>
@@ -1330,7 +1229,7 @@
     </row>
     <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="20">
         <v>45741.873819444445</v>
@@ -1351,13 +1250,13 @@
     </row>
     <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6">
         <v>45738.54011574074</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>9</v>
@@ -1372,13 +1271,13 @@
     </row>
     <row r="10" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="13">
         <v>45738.54011574074</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>9</v>
@@ -1393,13 +1292,13 @@
     </row>
     <row r="11" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="13">
         <v>45736.449456018519</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>9</v>
@@ -1414,13 +1313,13 @@
     </row>
     <row r="12" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B12" s="16">
         <v>45735.721805555557</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>9</v>
@@ -1435,13 +1334,13 @@
     </row>
     <row r="13" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B13" s="16">
         <v>45735.721805555557</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>9</v>
@@ -1456,13 +1355,13 @@
     </row>
     <row r="14" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>45735.711840277778</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>9</v>
@@ -1477,13 +1376,13 @@
     </row>
     <row r="15" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>45734.921365740738</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>9</v>
@@ -1498,7 +1397,7 @@
     </row>
     <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5">
         <v>45734.674560185187</v>
@@ -1519,13 +1418,13 @@
     </row>
     <row r="17" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B17" s="6">
         <v>45734.526979166665</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>9</v>
@@ -1540,13 +1439,13 @@
     </row>
     <row r="18" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18" s="16">
         <v>45734.526979166665</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>9</v>
@@ -1561,13 +1460,13 @@
     </row>
     <row r="19" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B19" s="13">
         <v>45732.580405092594</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>9</v>
@@ -1582,13 +1481,13 @@
     </row>
     <row r="20" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B20" s="13">
         <v>45730.847662037035</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>9</v>
@@ -1603,13 +1502,13 @@
     </row>
     <row r="21" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B21" s="13">
         <v>45730.539652777778</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>9</v>
@@ -1624,7 +1523,7 @@
     </row>
     <row r="22" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B22" s="16">
         <v>45723.693819444445</v>
@@ -1645,13 +1544,13 @@
     </row>
     <row r="23" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B23" s="13">
         <v>45721.40247685185</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>9</v>
@@ -1666,13 +1565,13 @@
     </row>
     <row r="24" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B24" s="16">
         <v>45720.435289351852</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>9</v>
@@ -1687,13 +1586,13 @@
     </row>
     <row r="25" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B25" s="13">
         <v>45720.426087962966</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
@@ -1708,13 +1607,13 @@
     </row>
     <row r="26" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B26" s="13">
         <v>45720.423842592594</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -1729,13 +1628,13 @@
     </row>
     <row r="27" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B27" s="16">
         <v>45717.533125000002</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>9</v>
@@ -1750,13 +1649,13 @@
     </row>
     <row r="28" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B28" s="16">
         <v>45717.533125000002</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>9</v>
@@ -1771,7 +1670,7 @@
     </row>
     <row r="29" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5">
         <v>45717.395555555559</v>
@@ -1792,13 +1691,13 @@
     </row>
     <row r="30" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B30" s="6">
         <v>45713.749050925922</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>9</v>
@@ -1813,13 +1712,13 @@
     </row>
     <row r="31" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B31" s="16">
         <v>45713.749050925922</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31" s="17" t="s">
         <v>9</v>
@@ -1834,7 +1733,7 @@
     </row>
     <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5">
         <v>45712.517372685186</v>
@@ -1855,7 +1754,7 @@
     </row>
     <row r="33" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B33" s="20">
         <v>45710.420763888891</v>
@@ -1876,7 +1775,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B34" s="20">
         <v>45709.729143518518</v>
@@ -1897,7 +1796,7 @@
     </row>
     <row r="35" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B35" s="6">
         <v>45709.727476851855</v>
@@ -1918,13 +1817,13 @@
     </row>
     <row r="36" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B36" s="13">
         <v>45709.714606481481</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>9</v>
@@ -1939,7 +1838,7 @@
     </row>
     <row r="37" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5">
         <v>45709.558576388888</v>
@@ -1960,7 +1859,7 @@
     </row>
     <row r="38" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B38" s="20">
         <v>45709.438148148147</v>
@@ -1981,7 +1880,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B39" s="20">
         <v>45709.437280092592</v>
@@ -2002,7 +1901,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B40" s="20">
         <v>45707.759733796294</v>
@@ -2023,7 +1922,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B41" s="20">
         <v>45707.706828703704</v>
@@ -2044,7 +1943,7 @@
     </row>
     <row r="42" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B42" s="6">
         <v>45707.706446759257</v>
@@ -2065,13 +1964,13 @@
     </row>
     <row r="43" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B43" s="13">
         <v>45707.467638888891</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>9</v>
@@ -2086,13 +1985,13 @@
     </row>
     <row r="44" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B44" s="13">
         <v>45707.467152777775</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>9</v>
@@ -2107,7 +2006,7 @@
     </row>
     <row r="45" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5">
         <v>45705.779699074075</v>
@@ -2128,7 +2027,7 @@
     </row>
     <row r="46" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B46" s="6">
         <v>45703.433368055557</v>
@@ -2149,13 +2048,13 @@
     </row>
     <row r="47" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B47" s="13">
         <v>45699.612754629627</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>9</v>
@@ -2170,13 +2069,13 @@
     </row>
     <row r="48" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B48" s="13">
         <v>45699.550081018519</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>9</v>
@@ -2191,13 +2090,13 @@
     </row>
     <row r="49" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B49" s="13">
         <v>45698.39025462963</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>9</v>
@@ -2212,7 +2111,7 @@
     </row>
     <row r="50" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B50" s="16">
         <v>45694.900439814817</v>
@@ -2233,13 +2132,13 @@
     </row>
     <row r="51" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B51" s="13">
         <v>45694.74927083333</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>9</v>
@@ -2254,13 +2153,13 @@
     </row>
     <row r="52" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B52" s="13">
         <v>45692.204386574071</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>9</v>
@@ -2275,13 +2174,13 @@
     </row>
     <row r="53" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B53" s="13">
         <v>45692.200011574074</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>9</v>
@@ -2296,7 +2195,7 @@
     </row>
     <row r="54" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B54" s="5">
         <v>45687.417222222219</v>
@@ -2317,7 +2216,7 @@
     </row>
     <row r="55" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B55" s="20">
         <v>45687.414085648146</v>
@@ -2338,13 +2237,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B56" s="6">
         <v>45686.84752314815</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>9</v>
@@ -2359,13 +2258,13 @@
     </row>
     <row r="57" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B57" s="16">
         <v>45686.84752314815</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>9</v>
@@ -2380,13 +2279,13 @@
     </row>
     <row r="58" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B58" s="13">
         <v>45686.846655092595</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>9</v>
@@ -2401,7 +2300,7 @@
     </row>
     <row r="59" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B59" s="5">
         <v>45686.424710648149</v>
@@ -2422,7 +2321,7 @@
     </row>
     <row r="60" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B60" s="20">
         <v>45686.401875000003</v>
@@ -2443,7 +2342,7 @@
     </row>
     <row r="61" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B61" s="6">
         <v>45685.376967592594</v>
@@ -2464,13 +2363,13 @@
     </row>
     <row r="62" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B62" s="13">
         <v>45683.708067129628</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>9</v>
@@ -2485,13 +2384,13 @@
     </row>
     <row r="63" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B63" s="13">
         <v>45680.744085648148</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>9</v>
@@ -2506,7 +2405,7 @@
     </row>
     <row r="64" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B64" s="5">
         <v>45679.577245370368</v>
@@ -2527,7 +2426,7 @@
     </row>
     <row r="65" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B65" s="20">
         <v>45679.575856481482</v>
@@ -2548,7 +2447,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="15" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B66" s="20">
         <v>45675.422824074078</v>
@@ -2569,7 +2468,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="15" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B67" s="20">
         <v>45672.734456018516</v>
@@ -2590,7 +2489,7 @@
     </row>
     <row r="68" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B68" s="20">
         <v>45667.415983796294</v>
@@ -2611,13 +2510,13 @@
     </row>
     <row r="69" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B69" s="13">
         <v>45666.692650462966</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>9</v>
@@ -2632,7 +2531,7 @@
     </row>
     <row r="70" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B70" s="5">
         <v>45664.523159722223</v>
@@ -2653,7 +2552,7 @@
     </row>
     <row r="71" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B71" s="20">
         <v>45662.940740740742</v>
@@ -2674,13 +2573,13 @@
     </row>
     <row r="72" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B72" s="16">
         <v>45662.883726851855</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" s="17" t="s">
         <v>9</v>
@@ -2695,13 +2594,13 @@
     </row>
     <row r="73" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B73" s="13">
         <v>45661.502013888887</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>9</v>
@@ -2716,13 +2615,13 @@
     </row>
     <row r="74" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B74" s="13">
         <v>45661.499537037038</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>9</v>
@@ -2737,7 +2636,7 @@
     </row>
     <row r="75" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B75" s="16">
         <v>45661.49894675926</v>
@@ -2756,108 +2655,138 @@
         <v>2425.71</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B76" s="25">
+    <row r="76" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="13">
         <v>45661.266250000001</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="29">
+        <v>140</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="14">
         <v>2030</v>
       </c>
-      <c r="F76" s="23"/>
-      <c r="G76" s="29">
+      <c r="F76" s="8"/>
+      <c r="G76" s="14">
         <v>2435.71</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="24"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="30"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B78" s="25">
+    <row r="77" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="13">
         <v>45660.49559027778</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="23"/>
-      <c r="F78" s="29">
+      <c r="C77" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="14">
         <v>-1600</v>
       </c>
-      <c r="G78" s="27">
+      <c r="G77" s="10">
         <v>438.71</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="24"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="28"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" s="25">
+    <row r="78" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="13">
         <v>45654.473101851851</v>
       </c>
-      <c r="C80" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" s="29">
+      <c r="C78" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="14">
         <v>1000</v>
       </c>
-      <c r="F80" s="23"/>
-      <c r="G80" s="29">
+      <c r="F78" s="8"/>
+      <c r="G78" s="14">
         <v>2038.71</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="24"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D81" s="24"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="30"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="16">
+        <v>45654.347592592596</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="17"/>
+      <c r="F79" s="18">
+        <v>-5</v>
+      </c>
+      <c r="G79" s="19">
+        <v>1038.71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="13">
+        <v>45645.388067129628</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="10">
+        <v>-530</v>
+      </c>
+      <c r="G80" s="14">
+        <v>1056.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="5">
+        <v>45645.387164351851</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="8"/>
+      <c r="F81" s="10">
+        <v>-27</v>
+      </c>
+      <c r="G81" s="14">
+        <v>1586.71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B82" s="16">
-        <v>45654.347592592596</v>
+        <v>86</v>
+      </c>
+      <c r="B82" s="20">
+        <v>45643.922303240739</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>8</v>
@@ -2867,423 +2796,585 @@
       </c>
       <c r="E82" s="17"/>
       <c r="F82" s="18">
+        <v>-20</v>
+      </c>
+      <c r="G82" s="19">
+        <v>1613.71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="6">
+        <v>45643.740706018521</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="17"/>
+      <c r="F83" s="18">
+        <v>-29</v>
+      </c>
+      <c r="G83" s="19">
+        <v>1633.71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="13">
+        <v>45643.740706018521</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="14">
+        <v>-2200</v>
+      </c>
+      <c r="G84" s="14">
+        <v>1662.71</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="13">
+        <v>45643.549375000002</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="14">
+        <v>3055</v>
+      </c>
+      <c r="F85" s="8"/>
+      <c r="G85" s="14">
+        <v>3862.71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="13">
+        <v>45629.683877314812</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="14">
+        <v>-1200</v>
+      </c>
+      <c r="G86" s="10">
+        <v>830.71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A87" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="13">
+        <v>45628.444953703707</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="14">
+        <v>2030</v>
+      </c>
+      <c r="F87" s="8"/>
+      <c r="G87" s="14">
+        <v>2030.71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="6">
+        <v>45627.77925925926</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="12"/>
+      <c r="F88" s="22">
+        <v>-8</v>
+      </c>
+      <c r="G88" s="22">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="13">
+        <v>45626.379537037035</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="14">
+        <v>-3699</v>
+      </c>
+      <c r="G89" s="10">
+        <v>58.71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="13">
+        <v>45626.377303240741</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="14">
+        <v>3699</v>
+      </c>
+      <c r="F90" s="8"/>
+      <c r="G90" s="14">
+        <v>3757.71</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="5">
+        <v>45626.375208333331</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="8"/>
+      <c r="F91" s="10">
         <v>-5</v>
       </c>
-      <c r="G82" s="19">
-        <v>1038.71</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="25">
-        <v>45645.388067129628</v>
-      </c>
-      <c r="C83" s="7" t="s">
+      <c r="G91" s="10">
+        <v>58.71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="20">
+        <v>45622.427523148152</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="17"/>
+      <c r="F92" s="18">
+        <v>-5</v>
+      </c>
+      <c r="G92" s="18">
+        <v>63.71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="20">
+        <v>45621.785729166666</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="17"/>
+      <c r="F93" s="18">
+        <v>-10</v>
+      </c>
+      <c r="G93" s="18">
+        <v>68.709999999999994</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="20">
+        <v>45621.780706018515</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="17"/>
+      <c r="F94" s="18">
+        <v>-70</v>
+      </c>
+      <c r="G94" s="18">
+        <v>78.709999999999994</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="6">
+        <v>45621.778333333335</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="17"/>
+      <c r="F95" s="18">
+        <v>-10</v>
+      </c>
+      <c r="G95" s="18">
+        <v>148.71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96" s="16">
+        <v>45621.778333333335</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="17"/>
+      <c r="F96" s="19">
+        <v>-1000</v>
+      </c>
+      <c r="G96" s="18">
+        <v>158.71</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="13">
+        <v>45621.776921296296</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="8"/>
+      <c r="F97" s="10">
+        <v>-830</v>
+      </c>
+      <c r="G97" s="14">
+        <v>1171.71</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A98" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="13">
+        <v>45621.739050925928</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="14">
+        <v>2000</v>
+      </c>
+      <c r="F98" s="8"/>
+      <c r="G98" s="14">
+        <v>2001.71</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="6">
+        <v>45618.432986111111</v>
+      </c>
+      <c r="C99" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D83" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="23"/>
-      <c r="F83" s="27">
-        <v>-530</v>
-      </c>
-      <c r="G83" s="29">
-        <v>1056.71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="24"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="30"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B85" s="5">
-        <v>45645.387164351851</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="23"/>
-      <c r="F85" s="27">
-        <v>-27</v>
-      </c>
-      <c r="G85" s="29">
-        <v>1586.71</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="31"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="34"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="24"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="28"/>
-      <c r="G87" s="30"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="20">
-        <v>45643.922303240739</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="17"/>
-      <c r="F88" s="18">
-        <v>-20</v>
-      </c>
-      <c r="G88" s="19">
-        <v>1613.71</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="6">
-        <v>45643.740706018521</v>
-      </c>
-      <c r="C89" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="17"/>
-      <c r="F89" s="18">
+      <c r="D99" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="12"/>
+      <c r="F99" s="22">
         <v>-29</v>
       </c>
-      <c r="G89" s="19">
-        <v>1633.71</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="25">
-        <v>45643.740706018521</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="23"/>
-      <c r="F90" s="29">
-        <v>-2200</v>
-      </c>
-      <c r="G90" s="29">
-        <v>1662.71</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="31"/>
-      <c r="B91" s="32"/>
-      <c r="C91" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D91" s="31"/>
-      <c r="E91" s="31"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="34"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="31"/>
-      <c r="B92" s="32"/>
-      <c r="C92" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D92" s="31"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="34"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="24"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D93" s="24"/>
-      <c r="E93" s="24"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="23" t="s">
+      <c r="G99" s="22">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B94" s="25">
-        <v>45643.549375000002</v>
-      </c>
-      <c r="C94" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D94" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="29">
-        <v>3055</v>
-      </c>
-      <c r="F94" s="23"/>
-      <c r="G94" s="29">
-        <v>3862.71</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="24"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" s="24"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="30"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96" s="23" t="s">
+      <c r="B100" s="13">
+        <v>45617.804351851853</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="14">
+        <v>1030</v>
+      </c>
+      <c r="F100" s="8"/>
+      <c r="G100" s="14">
+        <v>1030.71</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B96" s="25">
-        <v>45629.683877314812</v>
-      </c>
-      <c r="C96" s="7" t="s">
+      <c r="B101" s="5">
+        <v>45617.725590277776</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="8"/>
+      <c r="F101" s="10">
+        <v>-14</v>
+      </c>
+      <c r="G101" s="10">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" s="6">
+        <v>45616.440509259257</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="17"/>
+      <c r="F102" s="18">
+        <v>-30</v>
+      </c>
+      <c r="G102" s="18">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" s="13">
+        <v>45616.397094907406</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="8"/>
+      <c r="F103" s="14">
+        <v>-5000</v>
+      </c>
+      <c r="G103" s="10">
+        <v>101.71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" s="13">
+        <v>45615.911307870374</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="14">
+        <v>5100</v>
+      </c>
+      <c r="F104" s="8"/>
+      <c r="G104" s="14">
+        <v>5101.71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" s="16">
+        <v>45612.697858796295</v>
+      </c>
+      <c r="C105" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D96" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="23"/>
-      <c r="F96" s="29">
-        <v>-1200</v>
-      </c>
-      <c r="G96" s="27">
-        <v>830.71</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" s="24"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" s="24"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="28"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" s="25">
-        <v>45628.444953703707</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D98" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="29">
-        <v>2030</v>
-      </c>
-      <c r="F98" s="23"/>
-      <c r="G98" s="29">
-        <v>2030.71</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" s="24"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D99" s="24"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="30"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B100" s="6">
-        <v>45627.77925925926</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="12"/>
-      <c r="F100" s="22">
-        <v>-8</v>
-      </c>
-      <c r="G100" s="22">
+      <c r="D105" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="17"/>
+      <c r="F105" s="18">
+        <v>-29</v>
+      </c>
+      <c r="G105" s="18">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" s="13">
+        <v>45612.48201388889</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="14">
+        <v>1030</v>
+      </c>
+      <c r="F106" s="8"/>
+      <c r="G106" s="14">
+        <v>1030.71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" s="16">
+        <v>45611.748761574076</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="17"/>
+      <c r="F107" s="18">
+        <v>-5</v>
+      </c>
+      <c r="G107" s="18">
         <v>0.71</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A101" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B101" s="25">
-        <v>45626.379537037035</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="23"/>
-      <c r="F101" s="29">
-        <v>-3699</v>
-      </c>
-      <c r="G101" s="27">
-        <v>58.71</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="24"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="12">
-        <v>746209372</v>
-      </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="28"/>
-    </row>
-    <row r="103" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A103" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" s="25">
-        <v>45626.377303240741</v>
-      </c>
-      <c r="C103" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="29">
-        <v>3699</v>
-      </c>
-      <c r="F103" s="23"/>
-      <c r="G103" s="29">
-        <v>3757.71</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" s="24"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" s="24"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="30"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="23" t="s">
+    <row r="108" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B105" s="5">
-        <v>45626.375208333331</v>
-      </c>
-      <c r="C105" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="23"/>
-      <c r="F105" s="27">
-        <v>-5</v>
-      </c>
-      <c r="G105" s="27">
-        <v>58.71</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="31"/>
-      <c r="B106" s="20"/>
-      <c r="C106" s="31"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="33"/>
-      <c r="G106" s="33"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="31"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="31"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="31"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="33"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="31"/>
-      <c r="B108" s="20"/>
-      <c r="C108" s="31"/>
-      <c r="D108" s="31"/>
-      <c r="E108" s="31"/>
-      <c r="F108" s="33"/>
-      <c r="G108" s="33"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="24"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="24"/>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="28"/>
-      <c r="G109" s="28"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B108" s="16">
+        <v>45611.748761574076</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="17"/>
+      <c r="F108" s="18">
+        <v>-450</v>
+      </c>
+      <c r="G108" s="18">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="13">
+        <v>45611.74759259259</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="10">
+        <v>140</v>
+      </c>
+      <c r="F109" s="8"/>
+      <c r="G109" s="10">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B110" s="20">
-        <v>45622.427523148152</v>
+        <v>111</v>
+      </c>
+      <c r="B110" s="16">
+        <v>45608.934062499997</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>8</v>
@@ -3293,398 +3384,480 @@
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="18">
+        <v>-42</v>
+      </c>
+      <c r="G110" s="18">
+        <v>315.70999999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="16">
+        <v>45605.415833333333</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="17"/>
+      <c r="F111" s="19">
+        <v>-4686</v>
+      </c>
+      <c r="G111" s="18">
+        <v>357.71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="5">
+        <v>45605.395196759258</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="8"/>
+      <c r="F112" s="10">
+        <v>-30</v>
+      </c>
+      <c r="G112" s="14">
+        <v>5043.71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="13">
+        <v>45597.373344907406</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F113" s="8"/>
+      <c r="G113" s="14">
+        <v>6073.71</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B114" s="13">
+        <v>45597.23746527778</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="14">
+        <v>2050</v>
+      </c>
+      <c r="F114" s="8"/>
+      <c r="G114" s="14">
+        <v>5073.71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B115" s="13">
+        <v>45595.005543981482</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="8"/>
+      <c r="F115" s="14">
+        <v>-3699</v>
+      </c>
+      <c r="G115" s="14">
+        <v>3023.71</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="13">
+        <v>45595.003344907411</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="14">
+        <v>3700</v>
+      </c>
+      <c r="F116" s="8"/>
+      <c r="G116" s="14">
+        <v>6722.71</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="13">
+        <v>45590.809861111113</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="14">
+        <v>2050</v>
+      </c>
+      <c r="F117" s="8"/>
+      <c r="G117" s="14">
+        <v>3022.71</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" s="13">
+        <v>45589.543761574074</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="8"/>
+      <c r="F118" s="14">
+        <v>-7500</v>
+      </c>
+      <c r="G118" s="14">
+        <v>1109.71</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" s="13">
+        <v>45589.49895833333</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="8"/>
+      <c r="F119" s="10">
+        <v>-530</v>
+      </c>
+      <c r="G119" s="14">
+        <v>8622.7099999999991</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="16">
+        <v>45589.496157407404</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="17"/>
+      <c r="F120" s="18">
+        <v>-10</v>
+      </c>
+      <c r="G120" s="19">
+        <v>9152.7099999999991</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="16">
+        <v>45589.496157407404</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="17"/>
+      <c r="F121" s="19">
+        <v>-1000</v>
+      </c>
+      <c r="G121" s="19">
+        <v>9162.7099999999991</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="13">
+        <v>45589.483368055553</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="14">
+        <v>10120</v>
+      </c>
+      <c r="F122" s="8"/>
+      <c r="G122" s="14">
+        <v>10162.709999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="41" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="13">
+        <v>45588.865810185183</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="10">
+        <v>33</v>
+      </c>
+      <c r="F123" s="8"/>
+      <c r="G123" s="10">
+        <v>42.71</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="13">
+        <v>45588.810370370367</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="8"/>
+      <c r="F124" s="14">
+        <v>-1600</v>
+      </c>
+      <c r="G124" s="10">
+        <v>42.71</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="13">
+        <v>45587.509143518517</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="8"/>
+      <c r="F125" s="10">
+        <v>-500</v>
+      </c>
+      <c r="G125" s="10">
+        <v>31.71</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="13">
+        <v>45587.469143518516</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="10">
+        <v>530</v>
+      </c>
+      <c r="F126" s="8"/>
+      <c r="G126" s="10">
+        <v>531.71</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="16">
+        <v>45582.743032407408</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="17"/>
+      <c r="F127" s="18">
+        <v>-29</v>
+      </c>
+      <c r="G127" s="18">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="13">
+        <v>45582.743032407408</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="8"/>
+      <c r="F128" s="10">
+        <v>-290</v>
+      </c>
+      <c r="G128" s="10">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="13">
+        <v>45581.863321759258</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="8"/>
+      <c r="F129" s="14">
+        <v>-3000</v>
+      </c>
+      <c r="G129" s="10">
+        <v>373.71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="13">
+        <v>45581.8278125</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="14">
+        <v>3300</v>
+      </c>
+      <c r="F130" s="8"/>
+      <c r="G130" s="14">
+        <v>3373.71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" s="13">
+        <v>45579.530763888892</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="8"/>
+      <c r="F131" s="14">
+        <v>-3200</v>
+      </c>
+      <c r="G131" s="10">
+        <v>126.71</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="16">
+        <v>45577.492858796293</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="17"/>
+      <c r="F132" s="18">
         <v>-5</v>
       </c>
-      <c r="G110" s="18">
-        <v>63.71</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B111" s="20">
-        <v>45621.785729166666</v>
-      </c>
-      <c r="C111" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="17"/>
-      <c r="F111" s="18">
-        <v>-10</v>
-      </c>
-      <c r="G111" s="18">
-        <v>68.709999999999994</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B112" s="20">
-        <v>45621.780706018515</v>
-      </c>
-      <c r="C112" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="17"/>
-      <c r="F112" s="18">
-        <v>-70</v>
-      </c>
-      <c r="G112" s="18">
-        <v>78.709999999999994</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" s="6">
-        <v>45621.778333333335</v>
-      </c>
-      <c r="C113" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="17"/>
-      <c r="F113" s="18">
-        <v>-10</v>
-      </c>
-      <c r="G113" s="18">
-        <v>148.71</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A114" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B114" s="16">
-        <v>45621.778333333335</v>
-      </c>
-      <c r="C114" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D114" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="17"/>
-      <c r="F114" s="19">
-        <v>-1000</v>
-      </c>
-      <c r="G114" s="18">
-        <v>158.71</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="25">
-        <v>45621.776921296296</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D115" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="23"/>
-      <c r="F115" s="27">
-        <v>-830</v>
-      </c>
-      <c r="G115" s="29">
-        <v>1171.71</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="24"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D116" s="24"/>
-      <c r="E116" s="24"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="30"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B117" s="25">
-        <v>45621.739050925928</v>
-      </c>
-      <c r="C117" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D117" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="29">
-        <v>2000</v>
-      </c>
-      <c r="F117" s="23"/>
-      <c r="G117" s="29">
-        <v>2001.71</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="31"/>
-      <c r="B118" s="32"/>
-      <c r="C118" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D118" s="31"/>
-      <c r="E118" s="34"/>
-      <c r="F118" s="31"/>
-      <c r="G118" s="34"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="24"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="24"/>
-      <c r="G119" s="30"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B120" s="6">
-        <v>45618.432986111111</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="12"/>
-      <c r="F120" s="22">
-        <v>-29</v>
-      </c>
-      <c r="G120" s="22">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B121" s="25">
-        <v>45617.804351851853</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D121" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="29">
-        <v>1030</v>
-      </c>
-      <c r="F121" s="23"/>
-      <c r="G121" s="29">
-        <v>1030.71</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="24"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D122" s="24"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="24"/>
-      <c r="G122" s="30"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B123" s="5">
-        <v>45617.725590277776</v>
-      </c>
-      <c r="C123" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="23"/>
-      <c r="F123" s="27">
-        <v>-14</v>
-      </c>
-      <c r="G123" s="27">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="24"/>
-      <c r="B124" s="6">
-        <v>45616.440509259257</v>
-      </c>
-      <c r="C124" s="24"/>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24"/>
-      <c r="F124" s="28"/>
-      <c r="G124" s="28"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B125" s="12"/>
-      <c r="C125" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="17"/>
-      <c r="F125" s="18">
-        <v>-30</v>
-      </c>
-      <c r="G125" s="18">
-        <v>14.71</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="B126" s="25">
-        <v>45616.397094907406</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D126" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="29">
-        <v>-5000</v>
-      </c>
-      <c r="G126" s="27">
-        <v>101.71</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="24"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D127" s="24"/>
-      <c r="E127" s="24"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="28"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B128" s="25">
-        <v>45615.911307870374</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="29">
-        <v>5100</v>
-      </c>
-      <c r="F128" s="23"/>
-      <c r="G128" s="29">
-        <v>5101.71</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="24"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" s="24"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="24"/>
-      <c r="G129" s="30"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B130" s="16">
-        <v>45612.697858796295</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="17"/>
-      <c r="F130" s="18">
-        <v>-29</v>
-      </c>
-      <c r="G130" s="18">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B131" s="25">
-        <v>45612.48201388889</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="29">
-        <v>1030</v>
-      </c>
-      <c r="F131" s="23"/>
-      <c r="G131" s="29">
-        <v>1030.71</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="24"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" s="24"/>
-      <c r="E132" s="30"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="30"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G132" s="18">
+        <v>126.71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B133" s="16">
-        <v>45611.748761574076</v>
+        <v>45577.492858796293</v>
       </c>
       <c r="C133" s="17" t="s">
         <v>13</v>
@@ -3694,1155 +3867,76 @@
       </c>
       <c r="E133" s="17"/>
       <c r="F133" s="18">
-        <v>-5</v>
+        <v>-500</v>
       </c>
       <c r="G133" s="18">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A134" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B134" s="16">
-        <v>45611.748761574076</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="17"/>
-      <c r="F134" s="18">
-        <v>-450</v>
-      </c>
-      <c r="G134" s="18">
-        <v>5.71</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A135" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B135" s="25">
-        <v>45611.74759259259</v>
+        <v>131.71</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" s="13">
+        <v>45576.817256944443</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="10">
+        <v>500</v>
+      </c>
+      <c r="F134" s="8"/>
+      <c r="G134" s="10">
+        <v>631.71</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" s="13">
+        <v>45576.77416666667</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="27">
-        <v>140</v>
-      </c>
-      <c r="F135" s="23"/>
-      <c r="G135" s="27">
-        <v>455.71</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136" s="24"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D136" s="24"/>
-      <c r="E136" s="28"/>
-      <c r="F136" s="24"/>
-      <c r="G136" s="28"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B137" s="16">
-        <v>45608.934062499997</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="17"/>
-      <c r="F137" s="18">
-        <v>-42</v>
-      </c>
-      <c r="G137" s="18">
-        <v>315.70999999999998</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A138" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B138" s="16">
-        <v>45605.415833333333</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D138" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" s="17"/>
-      <c r="F138" s="19">
-        <v>-4686</v>
-      </c>
-      <c r="G138" s="18">
-        <v>357.71</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B139" s="5">
-        <v>45605.395196759258</v>
-      </c>
-      <c r="C139" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="23"/>
-      <c r="F139" s="27">
-        <v>-30</v>
-      </c>
-      <c r="G139" s="29">
-        <v>5043.71</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="24"/>
-      <c r="B140" s="6">
-        <v>45604.44730324074</v>
-      </c>
-      <c r="C140" s="24"/>
-      <c r="D140" s="24"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="28"/>
-      <c r="G140" s="30"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B141" s="25">
-        <v>45597.373344907406</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D141" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F141" s="23"/>
-      <c r="G141" s="29">
-        <v>6073.71</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="24"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D142" s="24"/>
-      <c r="E142" s="30"/>
-      <c r="F142" s="24"/>
-      <c r="G142" s="30"/>
-    </row>
-    <row r="143" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A143" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="10">
+        <v>120</v>
+      </c>
+      <c r="F135" s="8"/>
+      <c r="G135" s="10">
+        <v>131.71</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B143" s="25">
-        <v>45597.23746527778</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D143" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" s="29">
-        <v>2050</v>
-      </c>
-      <c r="F143" s="23"/>
-      <c r="G143" s="29">
-        <v>5073.71</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" s="24"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D144" s="24"/>
-      <c r="E144" s="30"/>
-      <c r="F144" s="24"/>
-      <c r="G144" s="30"/>
-    </row>
-    <row r="145" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A145" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B145" s="25">
-        <v>45595.005543981482</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D145" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="23"/>
-      <c r="F145" s="29">
-        <v>-3699</v>
-      </c>
-      <c r="G145" s="29">
-        <v>3023.71</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146" s="24"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="12">
-        <v>746209372</v>
-      </c>
-      <c r="D146" s="24"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="30"/>
-      <c r="G146" s="30"/>
-    </row>
-    <row r="147" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A147" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B147" s="25">
-        <v>45595.003344907411</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D147" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="29">
-        <v>3700</v>
-      </c>
-      <c r="F147" s="23"/>
-      <c r="G147" s="29">
-        <v>6722.71</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148" s="24"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D148" s="24"/>
-      <c r="E148" s="30"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="30"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B149" s="25">
-        <v>45590.809861111113</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D149" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" s="29">
-        <v>2050</v>
-      </c>
-      <c r="F149" s="23"/>
-      <c r="G149" s="29">
-        <v>3022.71</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150" s="24"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D150" s="24"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="30"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A151" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B151" s="25">
-        <v>45589.543761574074</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D151" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="23"/>
-      <c r="F151" s="29">
-        <v>-7500</v>
-      </c>
-      <c r="G151" s="29">
-        <v>1109.71</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A152" s="31"/>
-      <c r="B152" s="32"/>
-      <c r="C152" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D152" s="31"/>
-      <c r="E152" s="31"/>
-      <c r="F152" s="34"/>
-      <c r="G152" s="34"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A153" s="24"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="30"/>
-      <c r="G153" s="30"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="B154" s="25">
-        <v>45589.49895833333</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D154" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="23"/>
-      <c r="F154" s="27">
-        <v>-530</v>
-      </c>
-      <c r="G154" s="29">
-        <v>8622.7099999999991</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155" s="24"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D155" s="24"/>
-      <c r="E155" s="24"/>
-      <c r="F155" s="28"/>
-      <c r="G155" s="30"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B156" s="16">
-        <v>45589.496157407404</v>
-      </c>
-      <c r="C156" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D156" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="17"/>
-      <c r="F156" s="18">
+      <c r="B136" s="5">
+        <v>45576.25</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="17"/>
+      <c r="F136" s="18">
         <v>-10</v>
       </c>
-      <c r="G156" s="19">
-        <v>9152.7099999999991</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A157" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B157" s="16">
-        <v>45589.496157407404</v>
-      </c>
-      <c r="C157" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D157" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="17"/>
-      <c r="F157" s="19">
-        <v>-1000</v>
-      </c>
-      <c r="G157" s="19">
-        <v>9162.7099999999991</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A158" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="B158" s="25">
-        <v>45589.483368055553</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D158" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="29">
-        <v>10120</v>
-      </c>
-      <c r="F158" s="23"/>
-      <c r="G158" s="29">
-        <v>10162.709999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A159" s="24"/>
-      <c r="B159" s="26"/>
-      <c r="C159" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D159" s="24"/>
-      <c r="E159" s="30"/>
-      <c r="F159" s="24"/>
-      <c r="G159" s="30"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A160" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B160" s="25">
-        <v>45588.865810185183</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D160" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="27">
-        <v>33</v>
-      </c>
-      <c r="F160" s="23"/>
-      <c r="G160" s="27">
-        <v>42.71</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A161" s="31"/>
-      <c r="B161" s="32"/>
-      <c r="C161" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D161" s="31"/>
-      <c r="E161" s="33"/>
-      <c r="F161" s="31"/>
-      <c r="G161" s="33"/>
-    </row>
-    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A162" s="24"/>
-      <c r="B162" s="26"/>
-      <c r="C162" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D162" s="24"/>
-      <c r="E162" s="28"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="28"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A163" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="B163" s="25">
-        <v>45588.810370370367</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D163" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" s="23"/>
-      <c r="F163" s="29">
-        <v>-1600</v>
-      </c>
-      <c r="G163" s="27">
-        <v>42.71</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A164" s="31"/>
-      <c r="B164" s="32"/>
-      <c r="C164" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="31"/>
-      <c r="E164" s="31"/>
-      <c r="F164" s="34"/>
-      <c r="G164" s="33"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165" s="24"/>
-      <c r="B165" s="26"/>
-      <c r="C165" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D165" s="24"/>
-      <c r="E165" s="24"/>
-      <c r="F165" s="30"/>
-      <c r="G165" s="28"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="B166" s="25">
-        <v>45587.509143518517</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D166" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="23"/>
-      <c r="F166" s="27">
-        <v>-500</v>
-      </c>
-      <c r="G166" s="27">
-        <v>31.71</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A167" s="31"/>
-      <c r="B167" s="32"/>
-      <c r="C167" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D167" s="31"/>
-      <c r="E167" s="31"/>
-      <c r="F167" s="33"/>
-      <c r="G167" s="33"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A168" s="31"/>
-      <c r="B168" s="32"/>
-      <c r="C168" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D168" s="31"/>
-      <c r="E168" s="31"/>
-      <c r="F168" s="33"/>
-      <c r="G168" s="33"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A169" s="24"/>
-      <c r="B169" s="26"/>
-      <c r="C169" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="D169" s="24"/>
-      <c r="E169" s="24"/>
-      <c r="F169" s="28"/>
-      <c r="G169" s="28"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A170" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="B170" s="25">
-        <v>45587.469143518516</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D170" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" s="27">
-        <v>530</v>
-      </c>
-      <c r="F170" s="23"/>
-      <c r="G170" s="27">
-        <v>531.71</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171" s="24"/>
-      <c r="B171" s="26"/>
-      <c r="C171" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D171" s="24"/>
-      <c r="E171" s="28"/>
-      <c r="F171" s="24"/>
-      <c r="G171" s="28"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B172" s="16">
-        <v>45582.743032407408</v>
-      </c>
-      <c r="C172" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D172" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="17"/>
-      <c r="F172" s="18">
-        <v>-29</v>
-      </c>
-      <c r="G172" s="18">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="B173" s="25">
-        <v>45582.743032407408</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D173" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" s="23"/>
-      <c r="F173" s="27">
-        <v>-290</v>
-      </c>
-      <c r="G173" s="27">
-        <v>30.71</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" s="31"/>
-      <c r="B174" s="32"/>
-      <c r="C174" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D174" s="31"/>
-      <c r="E174" s="31"/>
-      <c r="F174" s="33"/>
-      <c r="G174" s="33"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A175" s="31"/>
-      <c r="B175" s="32"/>
-      <c r="C175" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D175" s="31"/>
-      <c r="E175" s="31"/>
-      <c r="F175" s="33"/>
-      <c r="G175" s="33"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A176" s="24"/>
-      <c r="B176" s="26"/>
-      <c r="C176" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D176" s="24"/>
-      <c r="E176" s="24"/>
-      <c r="F176" s="28"/>
-      <c r="G176" s="28"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A177" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="B177" s="25">
-        <v>45581.863321759258</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D177" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" s="23"/>
-      <c r="F177" s="29">
-        <v>-3000</v>
-      </c>
-      <c r="G177" s="27">
-        <v>373.71</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A178" s="24"/>
-      <c r="B178" s="26"/>
-      <c r="C178" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D178" s="24"/>
-      <c r="E178" s="24"/>
-      <c r="F178" s="30"/>
-      <c r="G178" s="28"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A179" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="B179" s="25">
-        <v>45581.8278125</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D179" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" s="29">
-        <v>3300</v>
-      </c>
-      <c r="F179" s="23"/>
-      <c r="G179" s="29">
-        <v>3373.71</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A180" s="24"/>
-      <c r="B180" s="26"/>
-      <c r="C180" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D180" s="24"/>
-      <c r="E180" s="30"/>
-      <c r="F180" s="24"/>
-      <c r="G180" s="30"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A181" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B181" s="25">
-        <v>45579.530763888892</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D181" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" s="23"/>
-      <c r="F181" s="29">
-        <v>-3200</v>
-      </c>
-      <c r="G181" s="27">
-        <v>126.71</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182" s="24"/>
-      <c r="B182" s="26"/>
-      <c r="C182" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D182" s="24"/>
-      <c r="E182" s="24"/>
-      <c r="F182" s="30"/>
-      <c r="G182" s="28"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A183" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B183" s="16">
-        <v>45577.492858796293</v>
-      </c>
-      <c r="C183" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D183" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" s="17"/>
-      <c r="F183" s="18">
-        <v>-5</v>
-      </c>
-      <c r="G183" s="18">
-        <v>126.71</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A184" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B184" s="16">
-        <v>45577.492858796293</v>
-      </c>
-      <c r="C184" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D184" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E184" s="17"/>
-      <c r="F184" s="18">
-        <v>-500</v>
-      </c>
-      <c r="G184" s="18">
-        <v>131.71</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A185" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="B185" s="25">
-        <v>45576.817256944443</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D185" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="27">
-        <v>500</v>
-      </c>
-      <c r="F185" s="23"/>
-      <c r="G185" s="27">
-        <v>631.71</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A186" s="24"/>
-      <c r="B186" s="26"/>
-      <c r="C186" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D186" s="24"/>
-      <c r="E186" s="28"/>
-      <c r="F186" s="24"/>
-      <c r="G186" s="28"/>
-    </row>
-    <row r="187" spans="1:7" ht="20" x14ac:dyDescent="0.2">
-      <c r="A187" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B187" s="25">
-        <v>45576.77416666667</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D187" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="27">
-        <v>120</v>
-      </c>
-      <c r="F187" s="23"/>
-      <c r="G187" s="27">
-        <v>131.71</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188" s="24"/>
-      <c r="B188" s="26"/>
-      <c r="C188" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D188" s="24"/>
-      <c r="E188" s="28"/>
-      <c r="F188" s="24"/>
-      <c r="G188" s="28"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A189" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B189" s="5">
-        <v>45576.25</v>
-      </c>
-      <c r="C189" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D189" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="17"/>
-      <c r="F189" s="18">
-        <v>-10</v>
-      </c>
-      <c r="G189" s="18">
+      <c r="G136" s="18">
         <v>11.71</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="234">
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="F85:F87"/>
-    <mergeCell ref="G85:G87"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="E103:E104"/>
-    <mergeCell ref="F103:F104"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="F101:F102"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="E115:E116"/>
-    <mergeCell ref="F115:F116"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="A105:A109"/>
-    <mergeCell ref="C105:C109"/>
-    <mergeCell ref="D105:D109"/>
-    <mergeCell ref="E105:E109"/>
-    <mergeCell ref="F105:F109"/>
-    <mergeCell ref="G105:G109"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="D117:D119"/>
-    <mergeCell ref="E117:E119"/>
-    <mergeCell ref="F117:F119"/>
-    <mergeCell ref="G117:G119"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="E126:E127"/>
-    <mergeCell ref="F126:F127"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="D123:D124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="F123:F124"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="F131:F132"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="D135:D136"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="F135:F136"/>
-    <mergeCell ref="G135:G136"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="D143:D144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="F143:F144"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="D147:D148"/>
-    <mergeCell ref="E147:E148"/>
-    <mergeCell ref="F147:F148"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="D145:D146"/>
-    <mergeCell ref="E145:E146"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="G145:G146"/>
-    <mergeCell ref="A151:A153"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="D151:D153"/>
-    <mergeCell ref="E151:E153"/>
-    <mergeCell ref="F151:F153"/>
-    <mergeCell ref="G151:G153"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="D149:D150"/>
-    <mergeCell ref="E149:E150"/>
-    <mergeCell ref="F149:F150"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="F154:F155"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="A163:A165"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="D163:D165"/>
-    <mergeCell ref="E163:E165"/>
-    <mergeCell ref="F163:F165"/>
-    <mergeCell ref="G163:G165"/>
-    <mergeCell ref="A160:A162"/>
-    <mergeCell ref="B160:B162"/>
-    <mergeCell ref="D160:D162"/>
-    <mergeCell ref="E160:E162"/>
-    <mergeCell ref="F160:F162"/>
-    <mergeCell ref="G160:G162"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="F170:F171"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="G166:G169"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="E177:E178"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="G177:G178"/>
-    <mergeCell ref="A173:A176"/>
-    <mergeCell ref="B173:B176"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="E173:E176"/>
-    <mergeCell ref="F173:F176"/>
-    <mergeCell ref="G173:G176"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D181:D182"/>
-    <mergeCell ref="E181:E182"/>
-    <mergeCell ref="F181:F182"/>
-    <mergeCell ref="G181:G182"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="B179:B180"/>
-    <mergeCell ref="D179:D180"/>
-    <mergeCell ref="E179:E180"/>
-    <mergeCell ref="F179:F180"/>
-    <mergeCell ref="G179:G180"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="D187:D188"/>
-    <mergeCell ref="E187:E188"/>
-    <mergeCell ref="F187:F188"/>
-    <mergeCell ref="G187:G188"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="E185:E186"/>
-    <mergeCell ref="F185:F186"/>
-    <mergeCell ref="G185:G186"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datasets/MpesaStatement_Katra.xlsx
+++ b/datasets/MpesaStatement_Katra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/briankimanzi/Documents/programming Languages/PythonProgramming/JupyterNoteBook/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBE0ACB-0829-F243-9097-D05B8B443CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFD6FA5-BEDE-E24C-B9F5-330A51BB855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{5FAECA30-C9D0-45DB-B3FF-81CAF5B5014D}"/>
   </bookViews>
@@ -450,9 +450,6 @@
     <t>Pay Bill Online to 4103879 PAYSTACK PAYMENTS KENYA LIMITED Acc. Sand TI KE L</t>
   </si>
   <si>
-    <t xml:space="preserve"> Customer Transfer to -2547******581 ABDULLAHI SOYAN</t>
-  </si>
-  <si>
     <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB7D100D0B25.</t>
   </si>
   <si>
@@ -541,6 +538,9 @@
   </si>
   <si>
     <t>Business Payment from 149444 CO-OP BANK via API. Original conversation ID is OMNIRIB_AB5BBC296B24.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Customer Transfer to - 2547******581 ABDULLAHI SOYAN</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1298,7 @@
         <v>45736.449456018519</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>9</v>
@@ -1361,7 +1361,7 @@
         <v>45735.711840277778</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>9</v>
@@ -1382,7 +1382,7 @@
         <v>45734.921365740738</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>9</v>
@@ -1466,7 +1466,7 @@
         <v>45732.580405092594</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>9</v>
@@ -1487,7 +1487,7 @@
         <v>45730.847662037035</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>9</v>
@@ -1508,7 +1508,7 @@
         <v>45730.539652777778</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>9</v>
@@ -1550,7 +1550,7 @@
         <v>45721.40247685185</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>9</v>
@@ -1592,7 +1592,7 @@
         <v>45720.426087962966</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
@@ -1613,7 +1613,7 @@
         <v>45720.423842592594</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -1823,7 +1823,7 @@
         <v>45709.714606481481</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>9</v>
@@ -1970,7 +1970,7 @@
         <v>45707.467638888891</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>9</v>
@@ -1991,7 +1991,7 @@
         <v>45707.467152777775</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>9</v>
@@ -2054,7 +2054,7 @@
         <v>45699.612754629627</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>9</v>
@@ -2075,7 +2075,7 @@
         <v>45699.550081018519</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>9</v>
@@ -2096,7 +2096,7 @@
         <v>45698.39025462963</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>45694.74927083333</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>9</v>
@@ -2180,7 +2180,7 @@
         <v>45692.200011574074</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>9</v>
@@ -2285,7 +2285,7 @@
         <v>45686.846655092595</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>9</v>
@@ -2369,7 +2369,7 @@
         <v>45683.708067129628</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>9</v>
@@ -2390,7 +2390,7 @@
         <v>45680.744085648148</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>9</v>
@@ -2516,7 +2516,7 @@
         <v>45666.692650462966</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>9</v>
@@ -2600,7 +2600,7 @@
         <v>45661.502013888887</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>9</v>
@@ -2621,7 +2621,7 @@
         <v>45661.499537037038</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>9</v>
@@ -2663,7 +2663,7 @@
         <v>45661.266250000001</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>9</v>
@@ -2684,7 +2684,7 @@
         <v>45660.49559027778</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>9</v>
@@ -2705,7 +2705,7 @@
         <v>45654.473101851851</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>9</v>
@@ -2747,7 +2747,7 @@
         <v>45645.388067129628</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>9</v>
@@ -2831,7 +2831,7 @@
         <v>45643.740706018521</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>9</v>
@@ -2852,7 +2852,7 @@
         <v>45643.549375000002</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>9</v>
@@ -2873,7 +2873,7 @@
         <v>45629.683877314812</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>9</v>
@@ -2894,7 +2894,7 @@
         <v>45628.444953703707</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>9</v>
@@ -2957,7 +2957,7 @@
         <v>45626.377303240741</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>9</v>
@@ -3104,7 +3104,7 @@
         <v>45621.776921296296</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>9</v>
@@ -3125,7 +3125,7 @@
         <v>45621.739050925928</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>9</v>
@@ -3167,7 +3167,7 @@
         <v>45617.804351851853</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>9</v>
@@ -3230,7 +3230,7 @@
         <v>45616.397094907406</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>9</v>
@@ -3251,7 +3251,7 @@
         <v>45615.911307870374</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>9</v>
@@ -3293,7 +3293,7 @@
         <v>45612.48201388889</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>9</v>
@@ -3356,7 +3356,7 @@
         <v>45611.74759259259</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>9</v>
@@ -3440,7 +3440,7 @@
         <v>45597.373344907406</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>9</v>
@@ -3461,7 +3461,7 @@
         <v>45597.23746527778</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>9</v>
@@ -3503,7 +3503,7 @@
         <v>45595.003344907411</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>9</v>
@@ -3524,7 +3524,7 @@
         <v>45590.809861111113</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>9</v>
@@ -3545,7 +3545,7 @@
         <v>45589.543761574074</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>9</v>
@@ -3566,7 +3566,7 @@
         <v>45589.49895833333</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>9</v>
@@ -3629,7 +3629,7 @@
         <v>45589.483368055553</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>9</v>
@@ -3650,7 +3650,7 @@
         <v>45588.865810185183</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>9</v>
@@ -3671,7 +3671,7 @@
         <v>45588.810370370367</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>9</v>
@@ -3692,7 +3692,7 @@
         <v>45587.509143518517</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>9</v>
@@ -3713,7 +3713,7 @@
         <v>45587.469143518516</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>9</v>
@@ -3755,7 +3755,7 @@
         <v>45582.743032407408</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>9</v>
@@ -3776,7 +3776,7 @@
         <v>45581.863321759258</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>9</v>
@@ -3797,7 +3797,7 @@
         <v>45581.8278125</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>9</v>
@@ -3818,7 +3818,7 @@
         <v>45579.530763888892</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>9</v>
@@ -3881,7 +3881,7 @@
         <v>45576.817256944443</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D134" s="8" t="s">
         <v>9</v>
@@ -3902,7 +3902,7 @@
         <v>45576.77416666667</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D135" s="8" t="s">
         <v>9</v>

--- a/datasets/MpesaStatement_Katra.xlsx
+++ b/datasets/MpesaStatement_Katra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/briankimanzi/Documents/programming Languages/PythonProgramming/JupyterNoteBook/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFD6FA5-BEDE-E24C-B9F5-330A51BB855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D21BAD-A93F-E643-9344-8C1D113E40E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{5FAECA30-C9D0-45DB-B3FF-81CAF5B5014D}"/>
   </bookViews>
